--- a/artfynd/A 33044-2024 artfynd.xlsx
+++ b/artfynd/A 33044-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119312294</v>
+        <v>119312139</v>
       </c>
       <c r="B2" t="n">
-        <v>77910</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storstensvålen, Storstensvålen, Jmt</t>
+          <t>Storstensvålen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491776</v>
+        <v>491756</v>
       </c>
       <c r="R2" t="n">
-        <v>6943294</v>
+        <v>6943272</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,32 +786,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119311856</v>
+        <v>119311712</v>
       </c>
       <c r="B3" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -827,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491743</v>
+        <v>491748</v>
       </c>
       <c r="R3" t="n">
-        <v>6943357</v>
+        <v>6943360</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,31 +881,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119312052</v>
+        <v>119312048</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491770</v>
+        <v>491721</v>
       </c>
       <c r="R4" t="n">
-        <v>6943309</v>
+        <v>6943348</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,31 +988,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119312048</v>
+        <v>119312052</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491721</v>
+        <v>491770</v>
       </c>
       <c r="R5" t="n">
-        <v>6943348</v>
+        <v>6943309</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,31 +1095,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119311712</v>
+        <v>119312171</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491748</v>
+        <v>491718</v>
       </c>
       <c r="R6" t="n">
-        <v>6943360</v>
+        <v>6943334</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1177,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1187,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119312277</v>
+        <v>119312303</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,38 +1225,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storstensvålen, Storstensvålen, Jmt</t>
+          <t>Stenflon, Stenflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491705</v>
+        <v>491660</v>
       </c>
       <c r="R7" t="n">
-        <v>6943291</v>
+        <v>6943299</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1284,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1294,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,27 +1309,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Susanne Anderö Wännström</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Susanne Anderö Wännström</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119312203</v>
+        <v>119312539</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,34 +1332,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storstensvålen, Storstensvålen, Jmt</t>
+          <t>Stenflon, Stenflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491707</v>
+        <v>491637</v>
       </c>
       <c r="R8" t="n">
-        <v>6943297</v>
+        <v>6943242</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,49 +1416,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Susanne Anderö Wännström</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Susanne Anderö Wännström</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119313181</v>
+        <v>119313075</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491731</v>
+        <v>491723</v>
       </c>
       <c r="R9" t="n">
-        <v>6943322</v>
+        <v>6943321</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1498,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1508,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,32 +1535,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119311697</v>
+        <v>119313215</v>
       </c>
       <c r="B10" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1615,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491764</v>
+        <v>491728</v>
       </c>
       <c r="R10" t="n">
-        <v>6943337</v>
+        <v>6943354</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1605,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1615,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,66 +1630,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119311988</v>
+        <v>119312294</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenflon, Stenflon, Jmt</t>
+          <t>Storstensvålen, Storstensvålen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491779</v>
+        <v>491776</v>
       </c>
       <c r="R11" t="n">
-        <v>6943327</v>
+        <v>6943294</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,7 +1712,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,7 +1722,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,54 +1749,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119313124</v>
+        <v>119312695</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stenflon, Stenflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491731</v>
+        <v>491630</v>
       </c>
       <c r="R12" t="n">
-        <v>6943322</v>
+        <v>6943245</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1819,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1829,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,49 +1844,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119313074</v>
+        <v>119313286</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1959,13 +1891,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491718</v>
+        <v>491705</v>
       </c>
       <c r="R13" t="n">
-        <v>6943277</v>
+        <v>6943366</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,7 +1926,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2004,7 +1936,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,27 +1951,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119312918</v>
+        <v>119313181</v>
       </c>
       <c r="B14" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2047,21 +1974,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491703</v>
+        <v>491731</v>
       </c>
       <c r="R14" t="n">
-        <v>6943262</v>
+        <v>6943322</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,7 +2033,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2116,7 +2043,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,49 +2058,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119313177</v>
+        <v>119313277</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2183,10 +2105,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491711</v>
+        <v>491760</v>
       </c>
       <c r="R15" t="n">
-        <v>6943320</v>
+        <v>6943354</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2218,7 +2140,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2228,7 +2150,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,27 +2165,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119312139</v>
+        <v>119311988</v>
       </c>
       <c r="B16" t="n">
-        <v>91005</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2271,40 +2188,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storstensvålen, Jmt</t>
+          <t>Stenflon, Stenflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491756</v>
+        <v>491779</v>
       </c>
       <c r="R16" t="n">
-        <v>6943272</v>
+        <v>6943327</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2333,7 +2251,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2261,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,7 +2270,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2371,50 +2288,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119313286</v>
+        <v>119312203</v>
       </c>
       <c r="B17" t="n">
-        <v>78262</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stenflon, Stenflon, Jmt</t>
+          <t>Storstensvålen, Storstensvålen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491705</v>
+        <v>491707</v>
       </c>
       <c r="R17" t="n">
-        <v>6943366</v>
+        <v>6943297</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,7 +2358,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,7 +2368,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,62 +2383,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Susanne Anderö Wännström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Susanne Anderö Wännström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119312171</v>
+        <v>119312231</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenflon, Stenflon, Jmt</t>
+          <t>Storstensvålen, Storstensvålen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491718</v>
+        <v>491701</v>
       </c>
       <c r="R18" t="n">
-        <v>6943334</v>
+        <v>6943300</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2465,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2568,7 +2475,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,62 +2490,61 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Susanne Anderö Wännström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Susanne Anderö Wännström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119312303</v>
+        <v>119312277</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stenflon, Stenflon, Jmt</t>
+          <t>Storstensvålen, Storstensvålen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491660</v>
+        <v>491705</v>
       </c>
       <c r="R19" t="n">
-        <v>6943299</v>
+        <v>6943291</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2670,7 +2576,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2680,7 +2586,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,62 +2601,61 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Susanne Anderö Wännström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Susanne Anderö Wännström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119312702</v>
+        <v>119312278</v>
       </c>
       <c r="B20" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stenflon, Stenflon, Jmt</t>
+          <t>Storstensvålen, Storstensvålen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491735</v>
+        <v>491776</v>
       </c>
       <c r="R20" t="n">
-        <v>6943247</v>
+        <v>6943294</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2782,7 +2687,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2792,7 +2697,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,12 +2727,7 @@
         <v>119312535</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,37 +2835,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119313023</v>
+        <v>119313074</v>
       </c>
       <c r="B22" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>230405</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2975,13 +2870,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491714</v>
+        <v>491718</v>
       </c>
       <c r="R22" t="n">
-        <v>6943282</v>
+        <v>6943277</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3010,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,62 +2930,61 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119312695</v>
+        <v>119313124</v>
       </c>
       <c r="B23" t="n">
-        <v>78262</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stenflon, Stenflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491630</v>
+        <v>491731</v>
       </c>
       <c r="R23" t="n">
-        <v>6943245</v>
+        <v>6943322</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,7 +3016,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3026,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3147,49 +3041,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119312539</v>
+        <v>119313148</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3199,10 +3088,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491637</v>
+        <v>491705</v>
       </c>
       <c r="R24" t="n">
-        <v>6943242</v>
+        <v>6943310</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3234,7 +3123,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3133,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3271,37 +3160,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119313075</v>
+        <v>119313177</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3311,10 +3195,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491723</v>
+        <v>491711</v>
       </c>
       <c r="R25" t="n">
-        <v>6943321</v>
+        <v>6943320</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3346,7 +3230,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3356,7 +3240,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,27 +3255,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119313215</v>
+        <v>119312663</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3399,34 +3278,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stenflon, Stenflon, Jmt</t>
+          <t>Storstensvålen, Storstensvålen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491728</v>
+        <v>491751</v>
       </c>
       <c r="R26" t="n">
-        <v>6943354</v>
+        <v>6943266</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3458,7 +3337,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3468,7 +3347,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,15 +3374,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119313277</v>
+        <v>119312702</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,21 +3385,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3535,10 +3409,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491760</v>
+        <v>491735</v>
       </c>
       <c r="R27" t="n">
-        <v>6943354</v>
+        <v>6943247</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3570,7 +3444,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3580,7 +3454,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3607,54 +3481,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119312278</v>
+        <v>119312918</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Storstensvålen, Storstensvålen, Jmt</t>
+          <t>Stenflon, Stenflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491776</v>
+        <v>491703</v>
       </c>
       <c r="R28" t="n">
-        <v>6943294</v>
+        <v>6943262</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3686,7 +3551,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3696,7 +3561,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3711,27 +3576,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119313148</v>
+        <v>119311697</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3739,21 +3599,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>230405</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3763,10 +3623,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491705</v>
+        <v>491764</v>
       </c>
       <c r="R29" t="n">
-        <v>6943310</v>
+        <v>6943337</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3798,7 +3658,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3808,7 +3668,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3835,15 +3695,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119312231</v>
+        <v>119311856</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,34 +3706,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>230405</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storstensvålen, Storstensvålen, Jmt</t>
+          <t>Stenflon, Stenflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491701</v>
+        <v>491743</v>
       </c>
       <c r="R30" t="n">
-        <v>6943300</v>
+        <v>6943357</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3910,7 +3765,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3920,7 +3775,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3935,62 +3790,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Susanne Anderö Wännström</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Susanne Anderö Wännström</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119312663</v>
+        <v>119313023</v>
       </c>
       <c r="B31" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>230405</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storstensvålen, Storstensvålen, Jmt</t>
+          <t>Stenflon, Stenflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491751</v>
+        <v>491714</v>
       </c>
       <c r="R31" t="n">
-        <v>6943266</v>
+        <v>6943282</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4022,7 +3872,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4032,7 +3882,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4047,12 +3897,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 33044-2024 artfynd.xlsx
+++ b/artfynd/A 33044-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312139</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119311712</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312048</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312052</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312171</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312303</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312539</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119313075</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1639,6 +1684,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119313215</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1746,6 +1796,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312294</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1853,6 +1908,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312695</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1960,6 +2020,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119313286</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2067,6 +2132,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119313181</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2174,6 +2244,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119313277</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2285,6 +2360,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119311988</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2392,6 +2472,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312203</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2499,6 +2584,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312231</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2610,6 +2700,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312277</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2721,6 +2816,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312278</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2832,6 +2932,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312535</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2939,6 +3044,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119313074</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3050,6 +3160,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119313124</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3157,6 +3272,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119313148</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3264,6 +3384,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119313177</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3371,6 +3496,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312663</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3478,6 +3608,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312702</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3585,6 +3720,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119312918</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3692,6 +3832,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119311697</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3799,6 +3944,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119311856</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3906,8 +4056,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119313023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>